--- a/ВАС/Карим/Lab1/Отчет_ВАС_Вариант4.xlsx
+++ b/ВАС/Карим/Lab1/Отчет_ВАС_Вариант4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kargt\Desktop\УЧЕБА\5 КУРС\stage5\ВАС\Карим\Lab1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F7B429-7B8D-425E-A803-1E87F3102CFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7830CDE7-895C-4171-B034-8FAD72CD7A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="274">
   <si>
     <t>МИНИСТЕРСТВО НАУКИ И ВЫСШЕГО ОБРАЗОВАНИЯ РОССИЙСКОЙ ФЕДЕРАЦИИ</t>
   </si>
@@ -317,102 +317,6 @@
   </si>
   <si>
     <t>5. ПАРАЛЛЕЛЬНЫЕ ВЫЧИСЛЕНИЯ, СИНХРОНИЗАЦИЯ И ЭФФЕКТИВНОСТЬ</t>
-  </si>
-  <si>
-    <t>5.3 Исследование ситуации гонки данных (Data Race) — 20 параллельных потоков без синхронизации:</t>
-  </si>
-  <si>
-    <t>№ запуска</t>
-  </si>
-  <si>
-    <t>Ns (на поток)</t>
-  </si>
-  <si>
-    <t>Потоков NTh</t>
-  </si>
-  <si>
-    <t>Ожидаемая сумма</t>
-  </si>
-  <si>
-    <t>Фактическая сумма S</t>
-  </si>
-  <si>
-    <t>Абсолютная ошибка</t>
-  </si>
-  <si>
-    <t>Потеря данных (%)</t>
-  </si>
-  <si>
-    <t>Время dT (c)</t>
-  </si>
-  <si>
-    <t>5.4 Синхронизация с помощью критической секции (Critical Section, Ns = 1 000 000, 20 потоков):</t>
-  </si>
-  <si>
-    <t>5.5 Оптимизированное суммирование с локальными переменными (Fast, Ns = 50 000 000, 20 потоков):</t>
-  </si>
-  <si>
-    <t>5.6 Сводное сравнение методов параллельного суммирования:</t>
-  </si>
-  <si>
-    <t>Метод реализации</t>
-  </si>
-  <si>
-    <t>Всего единиц N</t>
-  </si>
-  <si>
-    <t>Точность результата</t>
-  </si>
-  <si>
-    <t>Среднее время (с)</t>
-  </si>
-  <si>
-    <t>Оценка производительности</t>
-  </si>
-  <si>
-    <t>Последовательное суммирование (1 поток)</t>
-  </si>
-  <si>
-    <t>100% (Без ошибок)</t>
-  </si>
-  <si>
-    <t>Базовое время T1</t>
-  </si>
-  <si>
-    <t>Параллельное суммирование с гонкой (Race)</t>
-  </si>
-  <si>
-    <t>Потеря 90-95% данных!</t>
-  </si>
-  <si>
-    <t>Быстро, но результат полностью неверен</t>
-  </si>
-  <si>
-    <t>Параллельное с критической секцией (CS)</t>
-  </si>
-  <si>
-    <t>100% (Корректно)</t>
-  </si>
-  <si>
-    <t>Замедление в сотни раз из-за накладных расходов CS</t>
-  </si>
-  <si>
-    <t>Параллельное с локальными суммами (Fast)</t>
-  </si>
-  <si>
-    <t>Максимальная скорость, масштабируемость и надежность</t>
-  </si>
-  <si>
-    <t>Выводы по разделу 5:</t>
-  </si>
-  <si>
-    <t>1. В программе без синхронизации (Race condition) возникает конкуренция 20 потоков за переменную S в памяти, приводящая к потере 90–95% инкрементов.</t>
-  </si>
-  <si>
-    <t>2. Блокировка критической секцией на каждом шаге цикла (CS) решает проблему гонки, но порождает колоссальные накладные расходы синхронизации (15.5 с на всего 20 млн операций).</t>
-  </si>
-  <si>
-    <t>3. Накопление локальных сумм потоками с однократным добавлением в глобальную переменную через CS обеспечивает как 100% целостность данных, так и предельное быстродействие (0.003 с на 1 млрд операций).</t>
   </si>
   <si>
     <t>6. ЧИСЛЕННОЕ ИНТЕГРИРОВАНИЕ И ИССЛЕДОВАНИЕ ПОГРЕШНОСТЕЙ</t>
@@ -1112,6 +1016,48 @@
       <t xml:space="preserve"> линейно. Изменение маски сходства для однопоточного процесса не дает ускорения (S=1.0), так как параллелизм не реализован в коде программы. Эффективность использования выделенных процессорных ресурсов при этом падает пропорционально 1 / vCPU.</t>
     </r>
   </si>
+  <si>
+    <t>5.1 2 потока</t>
+  </si>
+  <si>
+    <t>1 поток</t>
+  </si>
+  <si>
+    <t>видим, что количество потоков уменьшилось на 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2 указание vCPU </t>
+  </si>
+  <si>
+    <t>цп 0</t>
+  </si>
+  <si>
+    <t>5.3 программа</t>
+  </si>
+  <si>
+    <t>Запуск</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>T, с</t>
+  </si>
+  <si>
+    <t>5.4 программа с критической секцией</t>
+  </si>
+  <si>
+    <t>заметим, что сумма всегда правильная, но время значительно увеличилось</t>
+  </si>
+  <si>
+    <t>5.5 взаимодействие потоков</t>
+  </si>
+  <si>
+    <t>каждый поток копит частичную сумму в своей локальной переменной и только в конце один раз прибавляет её к общей S через критическую секцию</t>
+  </si>
+  <si>
+    <t>5.6 эффективность распараллеливания</t>
+  </si>
 </sst>
 </file>
 
@@ -1122,12 +1068,20 @@
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1202,13 +1156,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1328,6 +1275,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1402,45 +1356,45 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1449,30 +1403,30 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1494,12 +1448,18 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1520,200 +1480,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="ru-RU"/>
-  <c:roundedCorners val="1"/>
-  <c:style val="10"/>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Сравнение времени выполнения методов суммирования (сек)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'6'!$E$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Среднее время (с)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="1"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'6'!$A$26:$A$29</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>Последовательное суммирование (1 поток)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Параллельное суммирование с гонкой (Race)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Параллельное с критической секцией (CS)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Параллельное с локальными суммами (Fast)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'6'!$E$26:$E$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.171</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>15.504300000000001</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3.0000000000000001E-3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3B70-441D-8204-808F3A7048F6}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="10"/>
-        <c:axId val="100"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="10"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU"/>
-                  <a:t>Метод реализации</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="100"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="100"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="ru-RU"/>
-                  <a:t>Время выполнения (сек)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="1"/>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="10"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
-  </c:chart>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2054,7 +1820,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -2354,7 +2120,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -3564,10 +3330,10 @@
       <xdr:rowOff>14915</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>267226</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>158033</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>685924</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3590,8 +3356,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9555480" y="2796215"/>
-          <a:ext cx="4069606" cy="2154798"/>
+          <a:off x="8923020" y="2872415"/>
+          <a:ext cx="3497704" cy="1851985"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3913,37 +3679,488 @@
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>56348</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>769621</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>40469</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Рисунок 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A29B9EB1-5A07-4AF9-9E13-99E3C3824273}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect r="48516"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="688808"/>
+          <a:ext cx="4884420" cy="1995801"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19165</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1036320</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>137161</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC17B202-6DCD-40CB-9758-DB8989D74774}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect r="45668"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1" y="3943465"/>
+          <a:ext cx="5151119" cy="1946796"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5760000" cy="3600000"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>4076700</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>106565</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Рисунок 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8D2938A-E581-4D4A-8355-D5514121D831}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7040881"/>
+          <a:ext cx="4076700" cy="2842144"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
-  </xdr:oneCellAnchor>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>82814</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>784860</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>88852</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4CFAE590-8862-456B-B58F-0B8D99D91745}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="2726954"/>
+          <a:ext cx="4899660" cy="554678"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>9740</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1049438</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Рисунок 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1A87F11-79D3-4529-86C8-0FE8855146FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5945720"/>
+          <a:ext cx="5164238" cy="698920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>26393</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>310481</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>167641</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Рисунок 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{895C8329-7AC5-4E14-BB88-0F0A5B966A57}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4141193" y="10149841"/>
+          <a:ext cx="2547228" cy="2720340"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>3677069</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Рисунок 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{51160A80-21BD-40D7-962D-3F02FD56CB51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="10157460"/>
+          <a:ext cx="3677069" cy="2712720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>678180</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>768</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>624189</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>111242</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Рисунок 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34208322-344B-4D9A-96A1-1B4C48D5F5E3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4792980" y="13251948"/>
+          <a:ext cx="5363829" cy="3219434"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>475735</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>120599</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Рисунок 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB095040-5E38-43B0-8025-6EA2DB580F69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="13251180"/>
+          <a:ext cx="4590535" cy="3229559"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>908390</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>563056</xdr:colOff>
+      <xdr:row>108</xdr:row>
+      <xdr:rowOff>4584</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Рисунок 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A677BE72-373E-42B5-B292-6F0A78BDC19C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="908390" y="16954500"/>
+          <a:ext cx="6032606" cy="2884944"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>891541</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>7621</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Рисунок 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F4DCB83-9C39-42F1-B3B8-C7BF715A240D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="891541" y="20238721"/>
+          <a:ext cx="6035039" cy="3017520"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4355,7 +4572,7 @@
     </row>
     <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.3">
@@ -4467,7 +4684,7 @@
     </row>
     <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.3">
       <c r="B32" s="1" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.3">
@@ -4559,7 +4776,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="E1" s="39" t="s">
         <v>23</v>
@@ -4567,7 +4784,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4709,12 +4926,12 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="26" t="s">
-        <v>220</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="C18">
         <v>8</v>
@@ -4722,94 +4939,94 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C19" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
-        <v>182</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B24" s="29" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C27" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>191</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C30" t="s">
-        <v>193</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C31" t="s">
-        <v>194</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A39" s="33" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B40" s="26" t="s">
-        <v>222</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -4819,82 +5036,82 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="C44" s="27" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>198</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="C48" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="C50" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C56" s="27" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="C62" s="27" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.3">
@@ -4902,52 +5119,52 @@
     </row>
     <row r="64" spans="2:3" ht="15" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="C64" s="27" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A68" s="33" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B69" s="26" t="s">
-        <v>223</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B70" s="27" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>226</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B71" t="s">
-        <v>227</v>
+        <v>195</v>
       </c>
       <c r="C71" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B72" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="C72" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="C73" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -4987,42 +5204,42 @@
     </row>
     <row r="3" spans="1:7" ht="106.2" x14ac:dyDescent="0.3">
       <c r="B3" s="34" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="B4" s="35" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B21" s="36" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -5061,7 +5278,7 @@
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E46" s="28">
         <v>-128</v>
@@ -5081,7 +5298,7 @@
         <v>8</v>
       </c>
       <c r="D47" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E47" s="28">
         <v>0</v>
@@ -5101,7 +5318,7 @@
         <v>16</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E48" s="37">
         <v>-32768</v>
@@ -5121,7 +5338,7 @@
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E49" s="28">
         <v>0</v>
@@ -5141,7 +5358,7 @@
         <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E50" s="37">
         <v>-2147483648</v>
@@ -5161,7 +5378,7 @@
         <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E51" s="28">
         <v>0</v>
@@ -5181,7 +5398,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E52" s="37">
         <v>-2147483648</v>
@@ -5201,7 +5418,7 @@
         <v>32</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E53" s="28">
         <v>0</v>
@@ -5221,7 +5438,7 @@
         <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="E54" s="37">
         <v>-9.2233720368547697E+18</v>
@@ -5241,7 +5458,7 @@
         <v>64</v>
       </c>
       <c r="D55" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="E55" s="28">
         <v>0</v>
@@ -5327,37 +5544,37 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="38" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B73" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B84" t="s">
-        <v>248</v>
+        <v>216</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>249</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -5372,7 +5589,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:I132"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="77" customWidth="1"/>
@@ -5385,7 +5602,7 @@
     <col min="8" max="8" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="40" t="s">
         <v>90</v>
       </c>
@@ -5393,107 +5610,107 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G16" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G17" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G18" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G19" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G22" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G23" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I22" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I23" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>262</v>
+        <v>230</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>263</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>264</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="C57" t="s">
-        <v>271</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C58" s="30" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="E58" s="30" t="s">
-        <v>270</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
@@ -5575,33 +5792,33 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
-        <v>272</v>
+        <v>240</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="38" t="s">
-        <v>273</v>
+        <v>241</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>274</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>275</v>
+        <v>243</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D95" s="30" t="s">
-        <v>269</v>
+        <v>237</v>
       </c>
       <c r="E95" s="30" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="F95" s="30" t="s">
-        <v>276</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -5612,7 +5829,7 @@
         <v>1000000000</v>
       </c>
       <c r="F96" s="30" t="s">
-        <v>277</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="4:6" x14ac:dyDescent="0.3">
@@ -5623,7 +5840,7 @@
         <v>5000000000</v>
       </c>
       <c r="F97" s="30" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.3">
@@ -5634,7 +5851,7 @@
         <v>10000000000</v>
       </c>
       <c r="F98" s="30" t="s">
-        <v>279</v>
+        <v>247</v>
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.3">
@@ -5645,45 +5862,45 @@
         <v>22000000000</v>
       </c>
       <c r="F99" s="30" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
     </row>
     <row r="102" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="4:6" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B120" s="30" t="s">
-        <v>268</v>
+        <v>236</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
       <c r="D120" s="30" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="E120" s="41" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="F120" s="30" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="G120" s="30" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="H120" s="30" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
@@ -5895,7 +6112,7 @@
     </row>
     <row r="130" spans="1:8" ht="18" x14ac:dyDescent="0.3">
       <c r="A130" s="43" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
@@ -5903,7 +6120,7 @@
     </row>
     <row r="132" spans="1:8" ht="72" x14ac:dyDescent="0.3">
       <c r="A132" s="29" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -5917,7 +6134,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -5925,9 +6142,10 @@
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="55" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21" x14ac:dyDescent="0.4">
@@ -5943,509 +6161,231 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G73" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="H73" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="I73" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="J73" s="30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G74" s="30">
         <v>1</v>
       </c>
-      <c r="B5">
-        <v>50000000</v>
-      </c>
-      <c r="C5">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>1000000000</v>
-      </c>
-      <c r="E5">
-        <v>100000000</v>
-      </c>
-      <c r="F5">
-        <v>900000000</v>
-      </c>
-      <c r="G5">
-        <v>0.9</v>
-      </c>
-      <c r="H5">
-        <v>0.25200000410000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="H74" s="30">
+        <v>20000000</v>
+      </c>
+      <c r="I74" s="30">
+        <v>180000000</v>
+      </c>
+      <c r="J74" s="30">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G75" s="30">
         <v>2</v>
       </c>
-      <c r="B6">
-        <v>50000000</v>
-      </c>
-      <c r="C6">
-        <v>20</v>
-      </c>
-      <c r="D6">
-        <v>1000000000</v>
-      </c>
-      <c r="E6">
-        <v>100000000</v>
-      </c>
-      <c r="F6">
-        <v>900000000</v>
-      </c>
-      <c r="G6">
-        <v>0.9</v>
-      </c>
-      <c r="H6">
-        <v>0.24799999589999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="H75" s="30">
+        <v>30000000</v>
+      </c>
+      <c r="I75" s="30">
+        <v>170000000</v>
+      </c>
+      <c r="J75" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G76" s="30">
         <v>3</v>
       </c>
-      <c r="B7">
-        <v>50000000</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7">
-        <v>1000000000</v>
-      </c>
-      <c r="E7">
-        <v>100000000</v>
-      </c>
-      <c r="F7">
-        <v>900000000</v>
-      </c>
-      <c r="G7">
-        <v>0.9</v>
-      </c>
-      <c r="H7">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="H76" s="30">
+        <v>30000000</v>
+      </c>
+      <c r="I76" s="30">
+        <v>170000000</v>
+      </c>
+      <c r="J76" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G77" s="30">
         <v>4</v>
       </c>
-      <c r="B8">
-        <v>50000000</v>
-      </c>
-      <c r="C8">
-        <v>20</v>
-      </c>
-      <c r="D8">
-        <v>1000000000</v>
-      </c>
-      <c r="E8">
-        <v>100000000</v>
-      </c>
-      <c r="F8">
-        <v>900000000</v>
-      </c>
-      <c r="G8">
-        <v>0.9</v>
-      </c>
-      <c r="H8">
-        <v>0.25799998639999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="H77" s="30">
+        <v>30000000</v>
+      </c>
+      <c r="I77" s="30">
+        <v>170000000</v>
+      </c>
+      <c r="J77" s="30">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G78" s="30">
         <v>5</v>
       </c>
-      <c r="B9">
-        <v>50000000</v>
-      </c>
-      <c r="C9">
-        <v>20</v>
-      </c>
-      <c r="D9">
-        <v>1000000000</v>
-      </c>
-      <c r="E9">
-        <v>50000000</v>
-      </c>
-      <c r="F9">
-        <v>950000000</v>
-      </c>
-      <c r="G9">
-        <v>0.95</v>
-      </c>
-      <c r="H9">
-        <v>0.2430000007</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>93</v>
-      </c>
-      <c r="B13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D13" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="H78" s="30">
+        <v>20000000</v>
+      </c>
+      <c r="I78" s="30">
+        <v>180000000</v>
+      </c>
+      <c r="J78" s="30">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>269</v>
+      </c>
+      <c r="B92" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G93" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="H93" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="I93" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="J93" s="30" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G94" s="30">
         <v>1</v>
       </c>
-      <c r="B14">
-        <v>1000000</v>
-      </c>
-      <c r="C14">
-        <v>20</v>
-      </c>
-      <c r="D14">
+      <c r="H94" s="30">
         <v>20000000</v>
       </c>
-      <c r="E14">
+      <c r="I94" s="30">
+        <v>0</v>
+      </c>
+      <c r="J94" s="30">
+        <v>1.4350000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G95" s="30">
+        <v>2</v>
+      </c>
+      <c r="H95" s="30">
         <v>20000000</v>
       </c>
-      <c r="F14">
+      <c r="I95" s="30">
         <v>0</v>
       </c>
-      <c r="G14">
+      <c r="J95" s="30">
+        <v>1.4490000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G96" s="30">
+        <v>3</v>
+      </c>
+      <c r="H96" s="30">
+        <v>20000000</v>
+      </c>
+      <c r="I96" s="30">
         <v>0</v>
       </c>
-      <c r="H14">
-        <v>15.666999816900001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>1000000</v>
-      </c>
-      <c r="C15">
-        <v>20</v>
-      </c>
-      <c r="D15">
+      <c r="J96" s="30">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G97" s="30">
+        <v>4</v>
+      </c>
+      <c r="H97" s="30">
         <v>20000000</v>
       </c>
-      <c r="E15">
+      <c r="I97" s="30">
+        <v>0</v>
+      </c>
+      <c r="J97" s="30">
+        <v>1.425</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G98" s="30">
+        <v>5</v>
+      </c>
+      <c r="H98" s="30">
         <v>20000000</v>
       </c>
-      <c r="F15">
+      <c r="I98" s="30">
         <v>0</v>
       </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>15.3280000687</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>3</v>
-      </c>
-      <c r="B16">
-        <v>1000000</v>
-      </c>
-      <c r="C16">
-        <v>20</v>
-      </c>
-      <c r="D16">
-        <v>20000000</v>
-      </c>
-      <c r="E16">
-        <v>20000000</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>15.517999649</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>93</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20">
-        <v>50000000</v>
-      </c>
-      <c r="C20">
-        <v>20</v>
-      </c>
-      <c r="D20">
-        <v>1000000000</v>
-      </c>
-      <c r="E20">
-        <v>1000000000</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="B21">
-        <v>50000000</v>
-      </c>
-      <c r="C21">
-        <v>20</v>
-      </c>
-      <c r="D21">
-        <v>1000000000</v>
-      </c>
-      <c r="E21">
-        <v>1000000000</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>3</v>
-      </c>
-      <c r="B22">
-        <v>50000000</v>
-      </c>
-      <c r="C22">
-        <v>20</v>
-      </c>
-      <c r="D22">
-        <v>1000000000</v>
-      </c>
-      <c r="E22">
-        <v>1000000000</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>3.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25" t="s">
-        <v>107</v>
-      </c>
-      <c r="F25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>109</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1000000000</v>
-      </c>
-      <c r="D26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26">
-        <v>1.171</v>
-      </c>
-      <c r="F26" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27">
-        <v>20</v>
-      </c>
-      <c r="C27">
-        <v>1000000000</v>
-      </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27">
-        <v>0.25</v>
-      </c>
-      <c r="F27" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>115</v>
-      </c>
-      <c r="B28">
-        <v>20</v>
-      </c>
-      <c r="C28">
-        <v>20000000</v>
-      </c>
-      <c r="D28" t="s">
-        <v>116</v>
-      </c>
-      <c r="E28">
-        <v>15.504300000000001</v>
-      </c>
-      <c r="F28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B29">
-        <v>20</v>
-      </c>
-      <c r="C29">
-        <v>1000000000</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
-      </c>
-      <c r="E29">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="F29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>123</v>
+      <c r="J98" s="30">
+        <v>1.266</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="38" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E111" s="44"/>
+      <c r="F111" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="G111" s="45"/>
+      <c r="H111" s="45"/>
+      <c r="I111" s="45"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F111:I111"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="H1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
     <hyperlink ref="F1" location="'2'!A3" display="Вернуться к оглавлению." xr:uid="{FEE5E5FF-2046-4EDA-B2DC-7B35AE08C3F1}"/>
@@ -6472,7 +6412,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>124</v>
+        <v>92</v>
       </c>
       <c r="C1" s="39" t="s">
         <v>23</v>
@@ -6483,32 +6423,32 @@
     </row>
     <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D5" s="16">
         <v>-5</v>
@@ -6530,7 +6470,7 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="D7" s="16">
         <v>-3</v>
@@ -6542,7 +6482,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="D8" s="16">
         <v>-2</v>
@@ -6554,7 +6494,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="D9" s="16">
         <v>-1</v>
@@ -6566,7 +6506,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
       <c r="D10" s="16">
         <v>0</v>
@@ -6578,7 +6518,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D11" s="16">
         <v>1</v>
@@ -6600,7 +6540,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="D13" s="16">
         <v>3</v>
@@ -6612,7 +6552,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="D14" s="16">
         <v>4</v>
@@ -6624,7 +6564,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="D15" s="16">
         <v>5</v>
@@ -6636,7 +6576,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="D16" s="16">
         <v>6</v>
@@ -6648,7 +6588,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="D17" s="16">
         <v>7</v>
@@ -6660,7 +6600,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="D18" s="16">
         <v>8</v>
@@ -6780,33 +6720,33 @@
     </row>
     <row r="33" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>146</v>
+        <v>114</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
@@ -6832,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
@@ -6858,7 +6798,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
@@ -6884,7 +6824,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -6910,7 +6850,7 @@
         <v>0</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
@@ -6936,7 +6876,7 @@
         <v>1E-3</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
@@ -6962,7 +6902,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
@@ -6988,7 +6928,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -7014,32 +6954,32 @@
         <v>0.42</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
-        <v>155</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -7068,7 +7008,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
-        <v>159</v>
+        <v>127</v>
       </c>
       <c r="D1" s="39" t="s">
         <v>23</v>
@@ -7079,33 +7019,33 @@
     </row>
     <row r="3" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>167</v>
+        <v>135</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -7240,32 +7180,32 @@
     </row>
     <row r="27" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
